--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCEA6B2-D971-4195-B02F-A1F8A73F649D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE866388-E98B-4818-8165-88F2649D3A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="87">
   <si>
     <t>type</t>
   </si>
@@ -287,12 +287,6 @@
   </si>
   <si>
     <t>${p_is_tra} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_state}</t>
-  </si>
-  <si>
-    <t>${p_location}</t>
   </si>
   <si>
     <t>Total Tetracycline received</t>
@@ -391,7 +385,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -414,6 +408,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -421,7 +445,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -445,15 +469,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -468,6 +483,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -753,11 +786,11 @@
     <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.25" style="5" customWidth="1"/>
     <col min="3" max="3" width="42.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="5" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
     <col min="6" max="6" width="12" style="5" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="30.125" style="5" customWidth="1"/>
     <col min="9" max="9" width="19.625" style="5" customWidth="1"/>
     <col min="10" max="10" width="9.75" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.625" style="5" customWidth="1"/>
@@ -771,95 +804,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="4" customFormat="1" ht="31.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
       <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="15" t="s">
         <v>37</v>
       </c>
       <c r="Q2" s="8"/>
@@ -892,12 +925,10 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="9" t="s">
-        <v>84</v>
-      </c>
+      <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
@@ -927,13 +958,11 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="15" t="s">
         <v>39</v>
       </c>
       <c r="Q4" s="9"/>
-      <c r="R4" s="9" t="s">
-        <v>85</v>
-      </c>
+      <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
@@ -962,14 +991,12 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="15" t="s">
         <v>40</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="9" t="s">
-        <v>85</v>
-      </c>
+      <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
     </row>
@@ -1142,7 +1169,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="21" t="s">
         <v>78</v>
       </c>
       <c r="I11" s="9"/>
@@ -1161,7 +1188,7 @@
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" ht="31.5">
       <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
@@ -1175,7 +1202,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="21" t="s">
         <v>79</v>
       </c>
       <c r="I12" s="9"/>
@@ -1208,7 +1235,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="21" t="s">
         <v>80</v>
       </c>
       <c r="I13" s="9"/>
@@ -1227,7 +1254,7 @@
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" ht="31.5">
       <c r="A14" s="9" t="s">
         <v>13</v>
       </c>
@@ -1241,7 +1268,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="21" t="s">
         <v>77</v>
       </c>
       <c r="I14" s="9"/>
@@ -1274,7 +1301,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="21" t="s">
         <v>76</v>
       </c>
       <c r="I15" s="9"/>
@@ -1307,7 +1334,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="21" t="s">
         <v>83</v>
       </c>
       <c r="I16" s="9"/>
@@ -1331,16 +1358,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="21" t="s">
         <v>83</v>
       </c>
       <c r="I17" s="9"/>
@@ -1367,13 +1394,13 @@
         <v>72</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="21" t="s">
         <v>83</v>
       </c>
       <c r="I18" s="9"/>

--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE866388-E98B-4818-8165-88F2649D3A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3371A26A-3694-49BC-AA3D-141AC78BE3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
   <si>
     <t>type</t>
   </si>
@@ -85,9 +85,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>select_one yes_no</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
@@ -157,30 +154,9 @@
     <t>col_3</t>
   </si>
   <si>
-    <t>col_4</t>
-  </si>
-  <si>
     <t>required_message::English</t>
   </si>
   <si>
-    <t>(Demo) 2. MDA Medicine Receipt Form</t>
-  </si>
-  <si>
-    <t>demo_mda_9999_2_part</t>
-  </si>
-  <si>
-    <t>Is the district concerned to ONCHO</t>
-  </si>
-  <si>
-    <t>Is the district concerned to LF</t>
-  </si>
-  <si>
-    <t>Is the district concerned to SCHISTO</t>
-  </si>
-  <si>
-    <t>Is the district concerned to STH</t>
-  </si>
-  <si>
     <t>Total Praziquantel received</t>
   </si>
   <si>
@@ -205,36 +181,12 @@
     <t>Select District / LGA / County</t>
   </si>
   <si>
-    <t>Enter the village / location / site</t>
-  </si>
-  <si>
-    <t>Enter the ID of village / location / site</t>
-  </si>
-  <si>
     <t>p_state</t>
   </si>
   <si>
     <t>p_district</t>
   </si>
   <si>
-    <t>p_location</t>
-  </si>
-  <si>
-    <t>p_location_id</t>
-  </si>
-  <si>
-    <t>p_is_oncho</t>
-  </si>
-  <si>
-    <t>p_is_lf</t>
-  </si>
-  <si>
-    <t>p_is_schisto</t>
-  </si>
-  <si>
-    <t>p_is_sth</t>
-  </si>
-  <si>
     <t>p_total_pzq</t>
   </si>
   <si>
@@ -280,12 +232,6 @@
     <t>${p_is_sth} = 'Yes'</t>
   </si>
   <si>
-    <t>p_is_tra</t>
-  </si>
-  <si>
-    <t>Is the district concerned to TRACHOMA</t>
-  </si>
-  <si>
     <t>${p_is_tra} = 'Yes'</t>
   </si>
   <si>
@@ -296,6 +242,162 @@
   </si>
   <si>
     <t>Total Azithromycin tablets received</t>
+  </si>
+  <si>
+    <t>(Demo) 2. MDA Medicine Receipt Form V2</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_2_part_v2</t>
+  </si>
+  <si>
+    <t>${p_district}</t>
+  </si>
+  <si>
+    <t>${p_state}</t>
+  </si>
+  <si>
+    <t>Disease covered by the TDM</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>ONCHO</t>
+  </si>
+  <si>
+    <t>SCHISTO</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>select_multiple disease</t>
+  </si>
+  <si>
+    <t>p_disease</t>
+  </si>
+  <si>
+    <t>IVM</t>
+  </si>
+  <si>
+    <t>IVM+ALB+DEC</t>
+  </si>
+  <si>
+    <t>TETRA TAB</t>
+  </si>
+  <si>
+    <t>TETRA SUSP</t>
+  </si>
+  <si>
+    <t>MEB</t>
+  </si>
+  <si>
+    <t>PZQ</t>
+  </si>
+  <si>
+    <t>PZQ+ALB</t>
+  </si>
+  <si>
+    <t>PZQ+MEB</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>select_multiple medicine</t>
+  </si>
+  <si>
+    <t>p_medicine</t>
+  </si>
+  <si>
+    <t>Select the meicine package</t>
+  </si>
+  <si>
+    <t>IVM+ALB</t>
+  </si>
+  <si>
+    <t>You cannot select a single medicine together with its combination version</t>
+  </si>
+  <si>
+    <t>TETRA.TAB</t>
+  </si>
+  <si>
+    <t>TETRA.SUSP</t>
+  </si>
+  <si>
+    <t>TRACHOMA</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF'))) and
+not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
+not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'TETRA.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
+not(selected(${p_medicine}, 'TETRA.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>Enter the Health facility / Sub district</t>
+  </si>
+  <si>
+    <t>p_health_facility</t>
+  </si>
+  <si>
+    <t>select_one recorder_id</t>
+  </si>
+  <si>
+    <t>p_recorder_id</t>
+  </si>
+  <si>
+    <t>Select the recorder ID</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
 </sst>
 </file>
@@ -367,7 +469,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -445,7 +547,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -501,6 +603,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -780,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
@@ -788,7 +905,7 @@
     <col min="3" max="3" width="42.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="5" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12" style="5" customWidth="1"/>
+    <col min="6" max="6" width="48.25" style="5" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
     <col min="8" max="8" width="30.125" style="5" customWidth="1"/>
     <col min="9" max="9" width="19.625" style="5" customWidth="1"/>
@@ -835,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L1" s="16" t="s">
         <v>10</v>
@@ -847,102 +964,94 @@
         <v>12</v>
       </c>
       <c r="O1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="Q1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="R1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="S1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="T1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="U1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="19" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+    </row>
+    <row r="3" spans="1:21" s="4" customFormat="1">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
       <c r="P3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9"/>
@@ -959,9 +1068,11 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
       <c r="P4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
@@ -972,10 +1083,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9"/>
@@ -992,39 +1103,33 @@
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>44</v>
-      </c>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="10"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="J6" s="8"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="P6" s="15"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -1033,13 +1138,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="9" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1055,27 +1160,31 @@
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="P7" s="15"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" ht="362.25">
       <c r="A8" s="9" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="F8" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="8" t="s">
@@ -1086,7 +1195,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="P8" s="15"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -1094,30 +1203,22 @@
       <c r="U8" s="9"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="10"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="J9" s="8"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="P9" s="15"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
@@ -1126,19 +1227,21 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="9"/>
+      <c r="H10" s="21" t="s">
+        <v>62</v>
+      </c>
       <c r="I10" s="9"/>
       <c r="J10" s="8" t="s">
         <v>14</v>
@@ -1155,22 +1258,22 @@
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" ht="31.5">
       <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
       <c r="H11" s="21" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="8" t="s">
@@ -1188,22 +1291,22 @@
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
     </row>
-    <row r="12" spans="1:21" ht="31.5">
+    <row r="12" spans="1:21">
       <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
       <c r="H12" s="21" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="8" t="s">
@@ -1221,22 +1324,22 @@
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" ht="31.5">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
       <c r="H13" s="21" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="8" t="s">
@@ -1254,22 +1357,22 @@
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
     </row>
-    <row r="14" spans="1:21" ht="31.5">
+    <row r="14" spans="1:21">
       <c r="A14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
       <c r="H14" s="21" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="8" t="s">
@@ -1292,17 +1395,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
       <c r="H15" s="21" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="8" t="s">
@@ -1325,17 +1428,17 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
       <c r="H16" s="21" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="8" t="s">
@@ -1358,17 +1461,17 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="21" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="8" t="s">
@@ -1388,24 +1491,22 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="21" t="s">
-        <v>83</v>
-      </c>
+      <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="8" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -1424,20 +1525,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="10"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
@@ -1452,10 +1549,10 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -1477,33 +1574,6 @@
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
     </row>
-    <row r="21" spans="1:21">
-      <c r="A21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1513,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="5" bestFit="1" customWidth="1"/>
@@ -1524,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -1534,33 +1604,346 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="11">
+        <v>99</v>
+      </c>
+      <c r="C14" s="26">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="26"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C16" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C30">
-    <sortCondition ref="B5:B30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C46">
+    <sortCondition ref="B19:B46"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1578,24 +1961,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3371A26A-3694-49BC-AA3D-141AC78BE3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F5D109-ABFB-4B23-8240-8B523262276D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="121">
   <si>
     <t>type</t>
   </si>
@@ -193,9 +193,6 @@
     <t>p_total_alb</t>
   </si>
   <si>
-    <t>p_total_mbz</t>
-  </si>
-  <si>
     <t>p_total_ivm</t>
   </si>
   <si>
@@ -217,24 +214,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>${p_is_lf} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_is_oncho} = 'Yes' or ${p_is_lf} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_is_schisto} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_is_oncho} = 'Yes' or ${p_is_lf} = 'Yes' or ${p_is_sth} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_is_sth} = 'Yes'</t>
-  </si>
-  <si>
-    <t>${p_is_tra} = 'Yes'</t>
-  </si>
-  <si>
     <t>Total Tetracycline received</t>
   </si>
   <si>
@@ -286,12 +265,6 @@
     <t>IVM+ALB+DEC</t>
   </si>
   <si>
-    <t>TETRA TAB</t>
-  </si>
-  <si>
-    <t>TETRA SUSP</t>
-  </si>
-  <si>
     <t>MEB</t>
   </si>
   <si>
@@ -322,16 +295,79 @@
     <t>You cannot select a single medicine together with its combination version</t>
   </si>
   <si>
-    <t>TETRA.TAB</t>
-  </si>
-  <si>
-    <t>TETRA.SUSP</t>
-  </si>
-  <si>
     <t>TRACHOMA</t>
   </si>
   <si>
     <t>ALB</t>
+  </si>
+  <si>
+    <t>Enter the Health facility / Sub district</t>
+  </si>
+  <si>
+    <t>p_health_facility</t>
+  </si>
+  <si>
+    <t>select_one recorder_id</t>
+  </si>
+  <si>
+    <t>p_recorder_id</t>
+  </si>
+  <si>
+    <t>Select the recorder ID</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>TETRA</t>
+  </si>
+  <si>
+    <t>AZM.TAB</t>
+  </si>
+  <si>
+    <t>AZM TAB</t>
+  </si>
+  <si>
+    <t>AZM.SUSP</t>
+  </si>
+  <si>
+    <t>AZM SUSP</t>
   </si>
   <si>
     <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
@@ -342,62 +378,36 @@
 not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
 not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
 not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'TETRA.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
-not(selected(${p_medicine}, 'TETRA.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))</t>
-  </si>
-  <si>
-    <t>Enter the Health facility / Sub district</t>
-  </si>
-  <si>
-    <t>p_health_facility</t>
-  </si>
-  <si>
-    <t>select_one recorder_id</t>
-  </si>
-  <si>
-    <t>p_recorder_id</t>
-  </si>
-  <si>
-    <t>Select the recorder ID</t>
-  </si>
-  <si>
-    <t>recorder_id</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
+not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
+not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))and
+not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>p_total_meb</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.TAB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'TETRA')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
   </si>
 </sst>
 </file>
@@ -577,7 +587,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -987,13 +997,13 @@
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1">
       <c r="A2" s="8" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="8"/>
@@ -1071,7 +1081,7 @@
         <v>37</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -1083,10 +1093,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9"/>
@@ -1107,7 +1117,7 @@
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
@@ -1138,13 +1148,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1167,23 +1177,23 @@
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
     </row>
-    <row r="8" spans="1:21" ht="362.25">
+    <row r="8" spans="1:21" ht="393.75">
       <c r="A8" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
       <c r="F8" s="21" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -1225,7 +1235,7 @@
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" ht="78.75">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -1240,7 +1250,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="10"/>
       <c r="H10" s="21" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="8" t="s">
@@ -1258,7 +1268,7 @@
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
     </row>
-    <row r="11" spans="1:21" ht="31.5">
+    <row r="11" spans="1:21" ht="110.25">
       <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
@@ -1273,7 +1283,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
       <c r="H11" s="21" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="8" t="s">
@@ -1291,12 +1301,12 @@
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" ht="47.25">
       <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>42</v>
@@ -1306,7 +1316,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
       <c r="H12" s="21" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="8" t="s">
@@ -1324,12 +1334,12 @@
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
     </row>
-    <row r="13" spans="1:21" ht="31.5">
+    <row r="13" spans="1:21" ht="78.75">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>43</v>
@@ -1339,7 +1349,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
       <c r="H13" s="21" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="8" t="s">
@@ -1357,12 +1367,12 @@
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" ht="31.5">
       <c r="A14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>44</v>
@@ -1372,7 +1382,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
       <c r="H14" s="21" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="8" t="s">
@@ -1390,12 +1400,12 @@
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" ht="31.5">
       <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>45</v>
@@ -1405,7 +1415,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
       <c r="H15" s="21" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="8" t="s">
@@ -1423,22 +1433,22 @@
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" ht="31.5">
       <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
       <c r="H16" s="21" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="8" t="s">
@@ -1461,17 +1471,17 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="21" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="8" t="s">
@@ -1494,10 +1504,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="9"/>
@@ -1506,7 +1516,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -1583,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="5" bestFit="1" customWidth="1"/>
@@ -1605,139 +1615,139 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>117</v>
-      </c>
       <c r="C13" s="25" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B14" s="11">
         <v>99</v>
@@ -1778,172 +1788,183 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C46">
-    <sortCondition ref="B19:B46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C47">
+    <sortCondition ref="B19:B47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1972,10 +1993,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F5D109-ABFB-4B23-8240-8B523262276D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598B881B-AF08-4AB9-9E6B-0A722029734F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -223,12 +223,6 @@
     <t>Total Azithromycin tablets received</t>
   </si>
   <si>
-    <t>(Demo) 2. MDA Medicine Receipt Form V2</t>
-  </si>
-  <si>
-    <t>demo_mda_9999_2_part_v2</t>
-  </si>
-  <si>
     <t>${p_district}</t>
   </si>
   <si>
@@ -408,6 +402,12 @@
   </si>
   <si>
     <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>(Demo) 2. MDA Medicine Receipt Form V2.1</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_2_part_v2_1</t>
   </si>
 </sst>
 </file>
@@ -997,13 +997,13 @@
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1">
       <c r="A2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>92</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="8"/>
@@ -1081,7 +1081,7 @@
         <v>37</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -1093,10 +1093,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
@@ -1148,13 +1148,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1179,21 +1179,21 @@
     </row>
     <row r="8" spans="1:21" ht="393.75">
       <c r="A8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
       <c r="F8" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -1250,7 +1250,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="10"/>
       <c r="H10" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="8" t="s">
@@ -1283,7 +1283,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
       <c r="H11" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="8" t="s">
@@ -1306,7 +1306,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>42</v>
@@ -1316,7 +1316,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
       <c r="H12" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="8" t="s">
@@ -1349,7 +1349,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
       <c r="H13" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="8" t="s">
@@ -1382,7 +1382,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
       <c r="H14" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="8" t="s">
@@ -1415,7 +1415,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
       <c r="H15" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="8" t="s">
@@ -1448,7 +1448,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
       <c r="H16" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="8" t="s">
@@ -1481,7 +1481,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="8" t="s">
@@ -1615,139 +1615,139 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>95</v>
-      </c>
       <c r="C3" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="11">
         <v>99</v>
@@ -1788,178 +1788,178 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598B881B-AF08-4AB9-9E6B-0A722029734F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71E0A59-8981-480C-B801-4779381CB767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={EE5A6214-1DD5-4300-B82A-50949313AF1A}</author>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{EE5A6214-1DD5-4300-B82A-50949313AF1A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Meicine to medicine</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="123">
   <si>
     <t>type</t>
   </si>
@@ -229,9 +247,6 @@
     <t>${p_state}</t>
   </si>
   <si>
-    <t>Disease covered by the TDM</t>
-  </si>
-  <si>
     <t>LF</t>
   </si>
   <si>
@@ -280,9 +295,6 @@
     <t>p_medicine</t>
   </si>
   <si>
-    <t>Select the meicine package</t>
-  </si>
-  <si>
     <t>IVM+ALB</t>
   </si>
   <si>
@@ -364,57 +376,104 @@
     <t>AZM SUSP</t>
   </si>
   <si>
-    <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
-not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO'))) and
-not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF'))) and
-not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
-not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
-not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))and
+    <t>p_total_meb</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.TAB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'TETRA')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>disease_filter</t>
+  </si>
+  <si>
+    <t>selected(${p_disease}, disease_filter)</t>
+  </si>
+  <si>
+    <t>Select the medicine package</t>
+  </si>
+  <si>
+    <t>not(
+  selected(${p_disease}, 'LF') and
+  selected(${p_disease}, 'ONCHO') and
+  selected(${p_medicine}, 'IVM')
+)
+and
+not(
+  selected(${p_disease}, 'STH') and
+  selected(${p_disease}, 'SCHISTO') and
+  (
+    selected(${p_medicine}, 'ALB') or
+    selected(${p_medicine}, 'MEB') or
+    selected(${p_medicine}, 'PZQ')
+  )
+)
+and
+not(
+  selected(${p_disease}, 'SCHISTO') and
+  not(selected(${p_disease}, 'STH')) and
+  (
+    selected(${p_medicine}, 'PZQ+ALB') or
+    selected(${p_medicine}, 'PZQ+MEB')
+  )
+)
+and
+not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO') and not(selected(${p_disease}, 'LF'))))
+and
+not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO')))
+and
+not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF')))
+and
+not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO')))
+and
+not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA')))
+and
+not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))
+and
 not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
   </si>
   <si>
-    <t>p_total_meb</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'AZM.TAB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'TETRA')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB')  or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
-  </si>
-  <si>
-    <t>(Demo) 2. MDA Medicine Receipt Form V2.1</t>
-  </si>
-  <si>
-    <t>demo_mda_9999_2_part_v2_1</t>
+    <t>Disease covered by the MDA</t>
+  </si>
+  <si>
+    <t>(Demo) 2. MDA Medicine Receipt Form V3</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_2_part_v3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -481,6 +540,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -557,7 +621,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -627,6 +691,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -647,6 +714,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Tinkitina Benjamin" id="{ED0CDB8C-466B-4332-AA2B-C9F2182C4AD5}" userId="c23755edcbb30cff" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -905,8 +978,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C8" dT="2026-04-01T11:45:18.64" personId="{ED0CDB8C-466B-4332-AA2B-C9F2182C4AD5}" id="{EE5A6214-1DD5-4300-B82A-50949313AF1A}">
+    <text>Meicine to medicine</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
@@ -997,13 +1078,13 @@
     </row>
     <row r="2" spans="1:21" s="4" customFormat="1">
       <c r="A2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="8"/>
@@ -1093,10 +1174,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9"/>
@@ -1148,13 +1229,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="C7" s="10" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1177,32 +1258,34 @@
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
     </row>
-    <row r="8" spans="1:21" ht="393.75">
+    <row r="8" spans="1:21" ht="409.5">
       <c r="A8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="C8" s="10" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
       <c r="F8" s="21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="11" t="s">
         <v>14</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="M8" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="15"/>
@@ -1247,10 +1330,9 @@
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
       <c r="G10" s="10"/>
       <c r="H10" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="8" t="s">
@@ -1283,7 +1365,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
       <c r="H11" s="21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="8" t="s">
@@ -1306,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>42</v>
@@ -1316,7 +1398,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
       <c r="H12" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="8" t="s">
@@ -1349,7 +1431,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
       <c r="H13" s="21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="8" t="s">
@@ -1382,7 +1464,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
       <c r="H14" s="21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="8" t="s">
@@ -1415,7 +1497,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
       <c r="H15" s="21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="8" t="s">
@@ -1448,7 +1530,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
       <c r="H16" s="21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="8" t="s">
@@ -1481,7 +1563,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="8" t="s">
@@ -1588,12 +1670,13 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="5" bestFit="1" customWidth="1"/>
@@ -1602,7 +1685,7 @@
     <col min="4" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
@@ -1612,142 +1695,145 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="C3" s="25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C4" s="25" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="24" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C5" s="25" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="24" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C6" s="25" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="24" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C7" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="24" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C8" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="24" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C9" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="24" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C10" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="24" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C11" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="24" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C12" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="24" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C13" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B14" s="11">
         <v>99</v>
@@ -1756,12 +1842,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="26"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
@@ -1772,7 +1858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
@@ -1783,183 +1869,216 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="5" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="B23" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="5" t="s">
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="5" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>77</v>
+      <c r="D35" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1993,10 +2112,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_2_part.xlsx
+++ b/Demo/MDA/demo_mda_9999_2_part.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71E0A59-8981-480C-B801-4779381CB767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3BCD9C-06D8-4C80-9C77-C88CA69E1CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>disease_filter</t>
-  </si>
-  <si>
-    <t>selected(${p_disease}, disease_filter)</t>
   </si>
   <si>
     <t>Select the medicine package</t>
@@ -467,6 +464,9 @@
   </si>
   <si>
     <t>demo_mda_9999_2_part_v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selected(${p_disease}, disease_filter)</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1235,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1266,12 +1266,12 @@
         <v>79</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
       <c r="F8" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>81</v>
@@ -1284,7 +1284,7 @@
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
